--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_321_R33.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_321_R33.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5884</v>
+        <v>5.3969</v>
       </c>
       <c r="E2" t="n">
-        <v>4.1688</v>
+        <v>4.8766</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4195</v>
+        <v>0.5203</v>
       </c>
       <c r="G2" t="n">
         <v>4.9316</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.1988</v>
+        <v>-0.3903</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.731</v>
+        <v>-0.0233</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4678</v>
+        <v>-0.367</v>
       </c>
       <c r="V2" t="n">
         <v>-0.5361</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5598</v>
+        <v>2.2972</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7805</v>
+        <v>0.9548</v>
       </c>
       <c r="F3" t="n">
-        <v>1.7793</v>
+        <v>1.3424</v>
       </c>
       <c r="G3" t="n">
         <v>4.6612</v>
@@ -688,13 +688,13 @@
         <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>0.829</v>
+        <v>-0.4336</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9831</v>
+        <v>0.1575</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1542</v>
+        <v>-0.5911</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4665</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.9353</v>
+        <v>1.8516</v>
       </c>
       <c r="E4" t="n">
-        <v>0.4216</v>
+        <v>0.5396</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5137</v>
+        <v>1.312</v>
       </c>
       <c r="G4" t="n">
         <v>-0.8294</v>
@@ -766,13 +766,13 @@
         <v>2.0876</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0756</v>
+        <v>-0.1592</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5421</v>
+        <v>-0.4242</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4665</v>
+        <v>0.2649</v>
       </c>
       <c r="V4" t="n">
         <v>2.1444</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. THEIS</t>
+          <t>T. TARPEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5052</v>
+        <v>0.8502999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1836</v>
+        <v>0.0694</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.6784</v>
+        <v>0.7809</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.5219</v>
+        <v>0.6656</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6196</v>
+        <v>0.5619</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1415</v>
+        <v>0.1038</v>
       </c>
       <c r="J5" t="n">
-        <v>2.0244</v>
+        <v>0.1008</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2722</v>
+        <v>0.1008</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2477</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.5464</v>
+        <v>0.5648</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.6526</v>
+        <v>0.461</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.8938</v>
+        <v>0.1038</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>0.4639</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="S5" t="n">
-        <v>1.9549</v>
+        <v>-0.2792</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2467</v>
+        <v>-0.0314</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7082000000000001</v>
+        <v>-0.2478</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>T. TARPEY</t>
+          <t>D. THEIS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.598</v>
+        <v>0.1912</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0485</v>
+        <v>2.0041</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6465</v>
+        <v>-1.8129</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6656</v>
+        <v>-1.5219</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5619</v>
+        <v>0.6196</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1038</v>
+        <v>-2.1415</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1008</v>
+        <v>2.0244</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1008</v>
+        <v>2.2722</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0.2477</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5648</v>
+        <v>-3.5464</v>
       </c>
       <c r="N6" t="n">
-        <v>0.461</v>
+        <v>-1.6526</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1038</v>
+        <v>-1.8938</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4639</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4639</v>
+        <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5316</v>
+        <v>0.6409</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>0.0672</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3822</v>
+        <v>0.5737</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6994</v>
+        <v>-0.3462</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2877</v>
+        <v>1.4057</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.9871</v>
+        <v>-1.7519</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9988</v>
@@ -1000,13 +1000,13 @@
         <v>1.1598</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5925</v>
+        <v>-1.2393</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9981</v>
+        <v>-0.8801</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5944</v>
+        <v>-0.3591</v>
       </c>
       <c r="V7" t="n">
         <v>1.8919</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BEGARIN</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9456</v>
+        <v>-1.6166</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5407</v>
+        <v>-1.1736</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4049</v>
+        <v>-0.443</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.2494</v>
+        <v>-2.2693</v>
       </c>
       <c r="H8" t="n">
-        <v>0.3171</v>
+        <v>-0.5796</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.5664</v>
+        <v>-1.6896</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.5777</v>
+        <v>0.2513</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4572</v>
+        <v>0.78</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.035</v>
+        <v>-0.5286999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.3284</v>
+        <v>-2.5205</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.1401</v>
+        <v>-1.3596</v>
       </c>
       <c r="O8" t="n">
-        <v>0.4685</v>
+        <v>-1.1609</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
         <v>-0.232</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9282</v>
+        <v>-0.4865</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1968</v>
+        <v>-0.5461</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.125</v>
+        <v>0.0595</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5361</v>
+        <v>-0.2525</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0722</v>
+        <v>-0.6468</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5361</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>J. BEGARIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.2235</v>
+        <v>-1.7104</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8813</v>
+        <v>-1.5407</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3422</v>
+        <v>-0.1697</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2693</v>
+        <v>-2.2494</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.5796</v>
+        <v>0.3171</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.6896</v>
+        <v>-2.5664</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2513</v>
+        <v>-2.5777</v>
       </c>
       <c r="K9" t="n">
-        <v>0.78</v>
+        <v>0.4572</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-3.035</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.5205</v>
+        <v>0.3284</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3596</v>
+        <v>-0.1401</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1609</v>
+        <v>0.4685</v>
       </c>
       <c r="P9" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
         <v>-0.232</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0934</v>
+        <v>-0.6929999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2538</v>
+        <v>0.1968</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1604</v>
+        <v>-0.8898</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2525</v>
+        <v>0.5361</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6468</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3943</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.1991</v>
+        <v>-3.7952</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.2751</v>
+        <v>-1.0392</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.924</v>
+        <v>-2.756</v>
       </c>
       <c r="G10" t="n">
         <v>-2.871</v>
@@ -1234,13 +1234,13 @@
         <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.256</v>
+        <v>-0.852</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.9709</v>
+        <v>-0.735</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V10" t="n">
         <v>-0.5361</v>
@@ -1267,25 +1267,25 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.1191</v>
+        <v>3.1188</v>
       </c>
       <c r="E11" t="n">
-        <v>6.096600000000001</v>
+        <v>6.096699999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9776</v>
+        <v>-2.9779</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4813999999999994</v>
+        <v>-0.4814000000000003</v>
       </c>
       <c r="H11" t="n">
-        <v>3.199400000000001</v>
+        <v>3.1994</v>
       </c>
       <c r="I11" t="n">
         <v>-3.6805</v>
       </c>
       <c r="J11" t="n">
-        <v>8.832700000000001</v>
+        <v>8.832699999999999</v>
       </c>
       <c r="K11" t="n">
         <v>6.173500000000001</v>
@@ -1300,13 +1300,13 @@
         <v>-2.9742</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.3398</v>
+        <v>-6.339799999999999</v>
       </c>
       <c r="P11" t="n">
         <v>4.6391</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.799</v>
+        <v>-5.798999999999999</v>
       </c>
       <c r="R11" t="n">
         <v>10.438</v>
@@ -1315,10 +1315,10 @@
         <v>-3.8922</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2187</v>
+        <v>-2.2186</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6736</v>
+        <v>-1.6738</v>
       </c>
       <c r="V11" t="n">
         <v>2.8534</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.6272</v>
+        <v>2.1444</v>
       </c>
       <c r="E12" t="n">
-        <v>1.4732</v>
+        <v>3.2672</v>
       </c>
       <c r="F12" t="n">
-        <v>1.154</v>
+        <v>-1.1228</v>
       </c>
       <c r="G12" t="n">
-        <v>1.2453</v>
+        <v>1.9808</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.9195</v>
+        <v>0.6592</v>
       </c>
       <c r="I12" t="n">
-        <v>2.1648</v>
+        <v>1.3216</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6954</v>
+        <v>3.1681</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.9474</v>
+        <v>1.3682</v>
       </c>
       <c r="L12" t="n">
-        <v>1.6428</v>
+        <v>1.7999</v>
       </c>
       <c r="M12" t="n">
-        <v>0.55</v>
+        <v>-1.1873</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0279</v>
+        <v>-0.709</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5221</v>
+        <v>-0.4783</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.5515</v>
+        <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S12" t="n">
-        <v>1.9334</v>
+        <v>0.5553</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2571</v>
+        <v>-0.1175</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3238</v>
+        <v>0.6728</v>
       </c>
       <c r="V12" t="n">
-        <v>1.0722</v>
+        <v>0.5361</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>1.6083</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9661</v>
+        <v>2.1319</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1427</v>
+        <v>0.2937</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8234</v>
+        <v>1.8382</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.5798</v>
+        <v>1.2453</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5377999999999999</v>
+        <v>-0.9195</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1176</v>
+        <v>2.1648</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.7762</v>
+        <v>0.6954</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7597</v>
+        <v>-0.9474</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.5359</v>
+        <v>1.6428</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1963</v>
+        <v>0.55</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.222</v>
+        <v>0.0279</v>
       </c>
       <c r="O13" t="n">
-        <v>0.4183</v>
+        <v>0.5221</v>
       </c>
       <c r="P13" t="n">
-        <v>0.4639</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="S13" t="n">
-        <v>2.3656</v>
+        <v>1.438</v>
       </c>
       <c r="T13" t="n">
-        <v>1.9189</v>
+        <v>1.0776</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4468</v>
+        <v>0.3605</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.2836</v>
+        <v>1.0722</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.2836</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.2293</v>
+        <v>0.8773</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6774</v>
+        <v>0.1991</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4481</v>
+        <v>0.6783</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9808</v>
+        <v>-0.5798</v>
       </c>
       <c r="H14" t="n">
-        <v>0.6592</v>
+        <v>0.5377999999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>1.3216</v>
+        <v>-1.1176</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1681</v>
+        <v>-0.7762</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3682</v>
+        <v>0.7597</v>
       </c>
       <c r="L14" t="n">
-        <v>1.7999</v>
+        <v>-1.5359</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.1873</v>
+        <v>0.1963</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.709</v>
+        <v>-0.222</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4783</v>
+        <v>0.4183</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0.4639</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.3598</v>
+        <v>1.2768</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7073</v>
+        <v>0.9752</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3475</v>
+        <v>0.3016</v>
       </c>
       <c r="V14" t="n">
-        <v>0.5361</v>
+        <v>-0.2836</v>
       </c>
       <c r="W14" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0722</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. NEBO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1965</v>
+        <v>0.3855</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0953</v>
+        <v>2.2605</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.8989</v>
+        <v>-1.875</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.9723000000000001</v>
+        <v>1.0926</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0289</v>
+        <v>-0.2258</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.9435</v>
+        <v>1.3183</v>
       </c>
       <c r="J15" t="n">
-        <v>1.3442</v>
+        <v>3.0554</v>
       </c>
       <c r="K15" t="n">
-        <v>1.2337</v>
+        <v>0.787</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1104</v>
+        <v>2.2685</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.3165</v>
+        <v>-1.9629</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2626</v>
+        <v>-1.0127</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.0539</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R15" t="n">
-        <v>0.232</v>
+        <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>1.9369</v>
+        <v>0.4373</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7512</v>
+        <v>-0.1687</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1857</v>
+        <v>0.606</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-1.6083</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>-0.3943</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6664</v>
+        <v>0.0815</v>
       </c>
       <c r="E16" t="n">
-        <v>2.7323</v>
+        <v>0.8627</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.0659</v>
+        <v>-0.7812</v>
       </c>
       <c r="G16" t="n">
-        <v>1.0926</v>
+        <v>0.2204</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.2258</v>
+        <v>0.1034</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3183</v>
+        <v>0.1171</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0554</v>
+        <v>1.1323</v>
       </c>
       <c r="K16" t="n">
-        <v>0.787</v>
+        <v>0.2759</v>
       </c>
       <c r="L16" t="n">
-        <v>2.2685</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.9629</v>
+        <v>-0.9119</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.0127</v>
+        <v>-0.1725</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.7393999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q16" t="n">
         <v>-0.232</v>
       </c>
       <c r="R16" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7183</v>
+        <v>-0.2291</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3031</v>
+        <v>-0.5737</v>
       </c>
       <c r="U16" t="n">
-        <v>0.4151</v>
+        <v>0.3446</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.6083</v>
+        <v>-0.1418</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3943</v>
+        <v>0.5361</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.214</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>J. NEBO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4911</v>
+        <v>-0.2677</v>
       </c>
       <c r="E17" t="n">
-        <v>0.3909</v>
+        <v>1.2697</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.882</v>
+        <v>-1.5374</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2204</v>
+        <v>-0.9723000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1034</v>
+        <v>-0.0289</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1171</v>
+        <v>-0.9435</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1323</v>
+        <v>1.3442</v>
       </c>
       <c r="K17" t="n">
-        <v>0.2759</v>
+        <v>1.2337</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8564000000000001</v>
+        <v>0.1104</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9119</v>
+        <v>-2.3165</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.1725</v>
+        <v>-1.2626</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.0539</v>
       </c>
       <c r="P17" t="n">
         <v>0.232</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8017</v>
+        <v>0.4727</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.0455</v>
+        <v>-0.0745</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2438</v>
+        <v>0.5472</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.6419</v>
+        <v>-0.4903</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4178</v>
+        <v>-0.3842</v>
       </c>
       <c r="G18" t="n">
         <v>-0.5149</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3589</v>
+        <v>-0.2074</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.224</v>
+        <v>-0.1061</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1349</v>
+        <v>-0.1013</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3239</v>
+        <v>-1.6283</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.3035</v>
+        <v>-1.0676</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.0204</v>
+        <v>-0.5607</v>
       </c>
       <c r="G19" t="n">
         <v>-1.4873</v>
@@ -1936,13 +1936,13 @@
         <v>0.9278</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3211</v>
+        <v>0.3745</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.326</v>
+        <v>-0.0901</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0048</v>
+        <v>0.4646</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2836</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5246</v>
+        <v>-2.1485</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.499</v>
+        <v>-2.4374</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0256</v>
+        <v>0.2889</v>
       </c>
       <c r="G20" t="n">
         <v>2.3518</v>
@@ -2014,13 +2014,13 @@
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6291</v>
+        <v>0.747</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5895</v>
+        <v>0.472</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0395</v>
+        <v>0.275</v>
       </c>
       <c r="V20" t="n">
         <v>-1.0722</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8229</v>
+        <v>-2.632</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.5075</v>
+        <v>-1.5639</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3154</v>
+        <v>-1.068</v>
       </c>
       <c r="G21" t="n">
         <v>-2.8553</v>
@@ -2092,13 +2092,13 @@
         <v>0.6959</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5913</v>
+        <v>0.5996</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6642</v>
+        <v>0.2794</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07290000000000001</v>
+        <v>0.3203</v>
       </c>
       <c r="V21" t="n">
         <v>-1.0722</v>
@@ -2125,16 +2125,16 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.1189</v>
+        <v>-1.546200000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>2.977799999999999</v>
+        <v>2.9779</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.0967</v>
+        <v>-4.523899999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4812999999999996</v>
+        <v>0.4812999999999992</v>
       </c>
       <c r="H22" t="n">
         <v>-3.1992</v>
@@ -2170,13 +2170,13 @@
         <v>5.798999999999999</v>
       </c>
       <c r="S22" t="n">
-        <v>3.892300000000001</v>
+        <v>5.4647</v>
       </c>
       <c r="T22" t="n">
-        <v>1.6738</v>
+        <v>1.6736</v>
       </c>
       <c r="U22" t="n">
-        <v>2.2184</v>
+        <v>3.7913</v>
       </c>
       <c r="V22" t="n">
         <v>-2.8534</v>
